--- a/artfynd/A 49184-2022 artfynd.xlsx
+++ b/artfynd/A 49184-2022 artfynd.xlsx
@@ -1447,7 +1447,7 @@
         <v>110875588</v>
       </c>
       <c r="B9" t="n">
-        <v>96820</v>
+        <v>96823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>110875591</v>
       </c>
       <c r="B10" t="n">
-        <v>96820</v>
+        <v>96823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49184-2022 artfynd.xlsx
+++ b/artfynd/A 49184-2022 artfynd.xlsx
@@ -1447,7 +1447,7 @@
         <v>110875588</v>
       </c>
       <c r="B9" t="n">
-        <v>96823</v>
+        <v>96824</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>110875591</v>
       </c>
       <c r="B10" t="n">
-        <v>96823</v>
+        <v>96824</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49184-2022 artfynd.xlsx
+++ b/artfynd/A 49184-2022 artfynd.xlsx
@@ -1447,7 +1447,7 @@
         <v>110875588</v>
       </c>
       <c r="B9" t="n">
-        <v>96824</v>
+        <v>96829</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>110875591</v>
       </c>
       <c r="B10" t="n">
-        <v>96824</v>
+        <v>96829</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
